--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1174"/>
+  <dimension ref="A1:R1178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66200,6 +66200,230 @@
         <v>5035295853</v>
       </c>
     </row>
+    <row r="1175">
+      <c r="A1175" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1175" t="n">
+        <v>48.2238</v>
+      </c>
+      <c r="C1175" t="n">
+        <v>186902.9980009871</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>81328.78215735799</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>268231.7801583451</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>57164.92014316583</v>
+      </c>
+      <c r="G1175" t="n">
+        <v>15027.01906527482</v>
+      </c>
+      <c r="H1175" t="n">
+        <v>5962.124718499994</v>
+      </c>
+      <c r="I1175" t="n">
+        <v>104078.7518196409</v>
+      </c>
+      <c r="J1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1175" t="n">
+        <v>4337.65312</v>
+      </c>
+      <c r="L1175" t="n">
+        <v>-4337.65312</v>
+      </c>
+      <c r="M1175" t="n">
+        <v>61835.10239757133</v>
+      </c>
+      <c r="N1175" t="n">
+        <v>66172.75551757134</v>
+      </c>
+      <c r="O1175" t="n">
+        <v>9013172795</v>
+      </c>
+      <c r="P1175" t="n">
+        <v>724659962</v>
+      </c>
+      <c r="Q1175" t="n">
+        <v>287516310</v>
+      </c>
+      <c r="R1175" t="n">
+        <v>5019072912</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B1176" t="n">
+        <v>48.2326</v>
+      </c>
+      <c r="C1176" t="n">
+        <v>186111.3406700033</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>80106.4900710308</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>266217.8307410341</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>55947.03673449078</v>
+      </c>
+      <c r="G1176" t="n">
+        <v>14986.88121726799</v>
+      </c>
+      <c r="H1176" t="n">
+        <v>5902.483797265751</v>
+      </c>
+      <c r="I1176" t="n">
+        <v>103710.6308803589</v>
+      </c>
+      <c r="J1176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1176" t="n">
+        <v>4217.92082</v>
+      </c>
+      <c r="L1176" t="n">
+        <v>-4217.92082</v>
+      </c>
+      <c r="M1176" t="n">
+        <v>61511.34477511064</v>
+      </c>
+      <c r="N1176" t="n">
+        <v>65729.26559511064</v>
+      </c>
+      <c r="O1176" t="n">
+        <v>8976633850</v>
+      </c>
+      <c r="P1176" t="n">
+        <v>722856247</v>
+      </c>
+      <c r="Q1176" t="n">
+        <v>284692140</v>
+      </c>
+      <c r="R1176" t="n">
+        <v>5002233375</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1177" t="n">
+        <v>48.3465</v>
+      </c>
+      <c r="C1177" t="n">
+        <v>183857.6593134974</v>
+      </c>
+      <c r="D1177" t="n">
+        <v>78305.42115768464</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>262163.080471182</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>54202.885317448</v>
+      </c>
+      <c r="G1177" t="n">
+        <v>14920.61557713588</v>
+      </c>
+      <c r="H1177" t="n">
+        <v>5890.415500605008</v>
+      </c>
+      <c r="I1177" t="n">
+        <v>102877.0016030116</v>
+      </c>
+      <c r="J1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1177" t="n">
+        <v>4330.50153</v>
+      </c>
+      <c r="L1177" t="n">
+        <v>-4330.50153</v>
+      </c>
+      <c r="M1177" t="n">
+        <v>60169.62663274488</v>
+      </c>
+      <c r="N1177" t="n">
+        <v>64500.12816274488</v>
+      </c>
+      <c r="O1177" t="n">
+        <v>8888874326</v>
+      </c>
+      <c r="P1177" t="n">
+        <v>721359541</v>
+      </c>
+      <c r="Q1177" t="n">
+        <v>284780973</v>
+      </c>
+      <c r="R1177" t="n">
+        <v>4973742958</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1178" t="n">
+        <v>48.3727</v>
+      </c>
+      <c r="C1178" t="n">
+        <v>185474.1003706636</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>78925.7593435967</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>264399.8597142603</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>54836.27810727952</v>
+      </c>
+      <c r="G1178" t="n">
+        <v>14892.44249338987</v>
+      </c>
+      <c r="H1178" t="n">
+        <v>5890.219814068679</v>
+      </c>
+      <c r="I1178" t="n">
+        <v>103833.0771695605</v>
+      </c>
+      <c r="J1178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1178" t="n">
+        <v>4337.32894</v>
+      </c>
+      <c r="L1178" t="n">
+        <v>-4337.32894</v>
+      </c>
+      <c r="M1178" t="n">
+        <v>60858.3608936446</v>
+      </c>
+      <c r="N1178" t="n">
+        <v>65195.6898336446</v>
+      </c>
+      <c r="O1178" t="n">
+        <v>8971883015</v>
+      </c>
+      <c r="P1178" t="n">
+        <v>720387653</v>
+      </c>
+      <c r="Q1178" t="n">
+        <v>284925836</v>
+      </c>
+      <c r="R1178" t="n">
+        <v>5022686292</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1182"/>
+  <dimension ref="A1:R1183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66660,6 +66660,62 @@
         <v>4869909377</v>
       </c>
     </row>
+    <row r="1183">
+      <c r="A1183" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1183" t="n">
+        <v>48.5585</v>
+      </c>
+      <c r="C1183" t="n">
+        <v>179601.1074683114</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>82524.2176961809</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>262125.3251644923</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>58118.97082900007</v>
+      </c>
+      <c r="G1183" t="n">
+        <v>14988.83340712748</v>
+      </c>
+      <c r="H1183" t="n">
+        <v>5549.372859540554</v>
+      </c>
+      <c r="I1183" t="n">
+        <v>100203.8165099828</v>
+      </c>
+      <c r="J1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1183" t="n">
+        <v>3766.99452</v>
+      </c>
+      <c r="L1183" t="n">
+        <v>-3766.99452</v>
+      </c>
+      <c r="M1183" t="n">
+        <v>58859.08469166061</v>
+      </c>
+      <c r="N1183" t="n">
+        <v>62626.07921166061</v>
+      </c>
+      <c r="O1183" t="n">
+        <v>8721160377</v>
+      </c>
+      <c r="P1183" t="n">
+        <v>727835267</v>
+      </c>
+      <c r="Q1183" t="n">
+        <v>269469222</v>
+      </c>
+      <c r="R1183" t="n">
+        <v>4865747024</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1183"/>
+  <dimension ref="A1:R1184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66704,6 +66704,62 @@
         <v>4865747024</v>
       </c>
     </row>
+    <row r="1184">
+      <c r="A1184" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1184" t="n">
+        <v>48.5779</v>
+      </c>
+      <c r="C1184" t="n">
+        <v>176112.7682958712</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>83361.44965097298</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>259474.2179468442</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>58965.94924852659</v>
+      </c>
+      <c r="G1184" t="n">
+        <v>14894.83024173544</v>
+      </c>
+      <c r="H1184" t="n">
+        <v>5481.908789799477</v>
+      </c>
+      <c r="I1184" t="n">
+        <v>102309.7508331978</v>
+      </c>
+      <c r="J1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1184" t="n">
+        <v>3754.76</v>
+      </c>
+      <c r="L1184" t="n">
+        <v>-3754.76</v>
+      </c>
+      <c r="M1184" t="n">
+        <v>53426.27843113843</v>
+      </c>
+      <c r="N1184" t="n">
+        <v>57181.03843113843</v>
+      </c>
+      <c r="O1184" t="n">
+        <v>8555188447</v>
+      </c>
+      <c r="P1184" t="n">
+        <v>723559574</v>
+      </c>
+      <c r="Q1184" t="n">
+        <v>266299617</v>
+      </c>
+      <c r="R1184" t="n">
+        <v>4969992845</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1184"/>
+  <dimension ref="A1:R1186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66772,6 +66772,118 @@
         <v>4969992845</v>
       </c>
     </row>
+    <row r="1185">
+      <c r="A1185" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1185" t="n">
+        <v>48.5873</v>
+      </c>
+      <c r="C1185" t="n">
+        <v>177148.1167506735</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>81380.77814572943</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>258528.894896403</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>56989.99742731125</v>
+      </c>
+      <c r="G1185" t="n">
+        <v>14872.27001706207</v>
+      </c>
+      <c r="H1185" t="n">
+        <v>5529.569681789274</v>
+      </c>
+      <c r="I1185" t="n">
+        <v>104175.450004425</v>
+      </c>
+      <c r="J1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1185" t="n">
+        <v>3789.69038</v>
+      </c>
+      <c r="L1185" t="n">
+        <v>-3789.69038</v>
+      </c>
+      <c r="M1185" t="n">
+        <v>52570.82704739716</v>
+      </c>
+      <c r="N1185" t="n">
+        <v>56360.51742739716</v>
+      </c>
+      <c r="O1185" t="n">
+        <v>8607148693</v>
+      </c>
+      <c r="P1185" t="n">
+        <v>722603445</v>
+      </c>
+      <c r="Q1185" t="n">
+        <v>268666861</v>
+      </c>
+      <c r="R1185" t="n">
+        <v>5061603842</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1186" t="n">
+        <v>48.6116</v>
+      </c>
+      <c r="C1186" t="n">
+        <v>176533.1264965564</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>79373.1702515449</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>255906.2967481012</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>54994.58203391783</v>
+      </c>
+      <c r="G1186" t="n">
+        <v>14773.30168108023</v>
+      </c>
+      <c r="H1186" t="n">
+        <v>5499.141624632804</v>
+      </c>
+      <c r="I1186" t="n">
+        <v>104443.3854676661</v>
+      </c>
+      <c r="J1186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1186" t="n">
+        <v>3776.09026</v>
+      </c>
+      <c r="L1186" t="n">
+        <v>-3776.09026</v>
+      </c>
+      <c r="M1186" t="n">
+        <v>51817.29772317718</v>
+      </c>
+      <c r="N1186" t="n">
+        <v>55593.38798317718</v>
+      </c>
+      <c r="O1186" t="n">
+        <v>8581557732</v>
+      </c>
+      <c r="P1186" t="n">
+        <v>718153832</v>
+      </c>
+      <c r="Q1186" t="n">
+        <v>267322073</v>
+      </c>
+      <c r="R1186" t="n">
+        <v>5077160077</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1189"/>
+  <dimension ref="A1:R1193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67031,6 +67031,230 @@
       </c>
       <c r="R1189" t="n">
         <v>5006630789</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1190" t="n">
+        <v>48.7671</v>
+      </c>
+      <c r="C1190" t="n">
+        <v>173718.5961642173</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>109640.4328533</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>173718.5961642173</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>50119.39075729334</v>
+      </c>
+      <c r="G1190" t="n">
+        <v>14740.64484047647</v>
+      </c>
+      <c r="H1190" t="n">
+        <v>5292.124034441253</v>
+      </c>
+      <c r="I1190" t="n">
+        <v>103566.4365320062</v>
+      </c>
+      <c r="J1190" t="n">
+        <v>800</v>
+      </c>
+      <c r="K1190" t="n">
+        <v>3814.106</v>
+      </c>
+      <c r="L1190" t="n">
+        <v>-3014.106</v>
+      </c>
+      <c r="M1190" t="n">
+        <v>50119.39075729334</v>
+      </c>
+      <c r="N1190" t="n">
+        <v>53133.49675729334</v>
+      </c>
+      <c r="O1190" t="n">
+        <v>8471752151</v>
+      </c>
+      <c r="P1190" t="n">
+        <v>718858501</v>
+      </c>
+      <c r="Q1190" t="n">
+        <v>258081542</v>
+      </c>
+      <c r="R1190" t="n">
+        <v>5050634767</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1191" t="n">
+        <v>48.7901</v>
+      </c>
+      <c r="C1191" t="n">
+        <v>170641.6343889436</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>109640.4328533</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>170641.6343889436</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>48329.27673851866</v>
+      </c>
+      <c r="G1191" t="n">
+        <v>14652.8421339575</v>
+      </c>
+      <c r="H1191" t="n">
+        <v>5139.852613542501</v>
+      </c>
+      <c r="I1191" t="n">
+        <v>102519.662902925</v>
+      </c>
+      <c r="J1191" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K1191" t="n">
+        <v>3668.77401</v>
+      </c>
+      <c r="L1191" t="n">
+        <v>-2368.77401</v>
+      </c>
+      <c r="M1191" t="n">
+        <v>48329.27673851866</v>
+      </c>
+      <c r="N1191" t="n">
+        <v>50698.05074851866</v>
+      </c>
+      <c r="O1191" t="n">
+        <v>8325622406</v>
+      </c>
+      <c r="P1191" t="n">
+        <v>714913633</v>
+      </c>
+      <c r="Q1191" t="n">
+        <v>250773923</v>
+      </c>
+      <c r="R1191" t="n">
+        <v>5001944605</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1192" t="n">
+        <v>48.9008</v>
+      </c>
+      <c r="C1192" t="n">
+        <v>171106.8191726925</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>109640.4328533</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>171106.8191726925</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>49836.37138860715</v>
+      </c>
+      <c r="G1192" t="n">
+        <v>14628.15731030985</v>
+      </c>
+      <c r="H1192" t="n">
+        <v>5129.336452573373</v>
+      </c>
+      <c r="I1192" t="n">
+        <v>101512.9540212021</v>
+      </c>
+      <c r="J1192" t="n">
+        <v>2400</v>
+      </c>
+      <c r="K1192" t="n">
+        <v>3850.41883</v>
+      </c>
+      <c r="L1192" t="n">
+        <v>-1450.41883</v>
+      </c>
+      <c r="M1192" t="n">
+        <v>49836.37138860715</v>
+      </c>
+      <c r="N1192" t="n">
+        <v>51286.79021860715</v>
+      </c>
+      <c r="O1192" t="n">
+        <v>8367260343</v>
+      </c>
+      <c r="P1192" t="n">
+        <v>715328595</v>
+      </c>
+      <c r="Q1192" t="n">
+        <v>250828656</v>
+      </c>
+      <c r="R1192" t="n">
+        <v>4964064662</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1193" t="n">
+        <v>48.9131</v>
+      </c>
+      <c r="C1193" t="n">
+        <v>169985.8662812212</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>109640.4328533</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>169985.8662812212</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>51188.65500244312</v>
+      </c>
+      <c r="G1193" t="n">
+        <v>14639.49522724996</v>
+      </c>
+      <c r="H1193" t="n">
+        <v>6700.95191267779</v>
+      </c>
+      <c r="I1193" t="n">
+        <v>97456.76413885033</v>
+      </c>
+      <c r="J1193" t="n">
+        <v>3650</v>
+      </c>
+      <c r="K1193" t="n">
+        <v>3649.3933</v>
+      </c>
+      <c r="L1193" t="n">
+        <v>0.6066999999998188</v>
+      </c>
+      <c r="M1193" t="n">
+        <v>51188.65500244312</v>
+      </c>
+      <c r="N1193" t="n">
+        <v>51188.04830244312</v>
+      </c>
+      <c r="O1193" t="n">
+        <v>8314535676</v>
+      </c>
+      <c r="P1193" t="n">
+        <v>716063094</v>
+      </c>
+      <c r="Q1193" t="n">
+        <v>327764331</v>
+      </c>
+      <c r="R1193" t="n">
+        <v>4766912450</v>
       </c>
     </row>
   </sheetData>
@@ -67044,7 +67268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D247"/>
+  <dimension ref="A1:D248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70513,6 +70737,20 @@
         <v>174404.765875</v>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B248" t="n">
+        <v>109640.4328533</v>
+      </c>
+      <c r="C248" t="n">
+        <v>61563.4089376</v>
+      </c>
+      <c r="D248" t="n">
+        <v>171203.8417909</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1198"/>
+  <dimension ref="A1:R1199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67535,6 +67535,62 @@
       </c>
       <c r="R1198" t="n">
         <v>4865444955</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1199" t="n">
+        <v>49.1091</v>
+      </c>
+      <c r="C1199" t="n">
+        <v>174724.1725260695</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>107062.0168102</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>174724.1725260695</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>51582.83147115301</v>
+      </c>
+      <c r="G1199" t="n">
+        <v>17496.35955454285</v>
+      </c>
+      <c r="H1199" t="n">
+        <v>7177.744918966138</v>
+      </c>
+      <c r="I1199" t="n">
+        <v>98467.23658140752</v>
+      </c>
+      <c r="J1199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1199" t="n">
+        <v>2876.40475</v>
+      </c>
+      <c r="L1199" t="n">
+        <v>-2876.40475</v>
+      </c>
+      <c r="M1199" t="n">
+        <v>51582.83147115301</v>
+      </c>
+      <c r="N1199" t="n">
+        <v>54459.23622115301</v>
+      </c>
+      <c r="O1199" t="n">
+        <v>8580546861</v>
+      </c>
+      <c r="P1199" t="n">
+        <v>859230471</v>
+      </c>
+      <c r="Q1199" t="n">
+        <v>352492593</v>
+      </c>
+      <c r="R1199" t="n">
+        <v>4835637368</v>
       </c>
     </row>
   </sheetData>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1199"/>
+  <dimension ref="A1:R1203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67591,6 +67591,230 @@
       </c>
       <c r="R1199" t="n">
         <v>4835637368</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1200" t="n">
+        <v>49.1267</v>
+      </c>
+      <c r="C1200" t="n">
+        <v>173813.0190303847</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>107008.1402781</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>173813.0190303847</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>52293.34783325563</v>
+      </c>
+      <c r="G1200" t="n">
+        <v>14491.53889839944</v>
+      </c>
+      <c r="H1200" t="n">
+        <v>7254.506958537821</v>
+      </c>
+      <c r="I1200" t="n">
+        <v>99773.62534019179</v>
+      </c>
+      <c r="J1200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1200" t="n">
+        <v>2980.97732</v>
+      </c>
+      <c r="L1200" t="n">
+        <v>-2980.97732</v>
+      </c>
+      <c r="M1200" t="n">
+        <v>52293.34783325563</v>
+      </c>
+      <c r="N1200" t="n">
+        <v>55274.32515325562</v>
+      </c>
+      <c r="O1200" t="n">
+        <v>8538860042</v>
+      </c>
+      <c r="P1200" t="n">
+        <v>711921484</v>
+      </c>
+      <c r="Q1200" t="n">
+        <v>356389987</v>
+      </c>
+      <c r="R1200" t="n">
+        <v>4901548960</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1201" t="n">
+        <v>49.1274</v>
+      </c>
+      <c r="C1201" t="n">
+        <v>174501.0158893001</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>107008.1402781</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>174501.0158893001</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>52459.68667179618</v>
+      </c>
+      <c r="G1201" t="n">
+        <v>14541.03056542785</v>
+      </c>
+      <c r="H1201" t="n">
+        <v>7186.392298391528</v>
+      </c>
+      <c r="I1201" t="n">
+        <v>100313.9063536845</v>
+      </c>
+      <c r="J1201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1201" t="n">
+        <v>3007.15854</v>
+      </c>
+      <c r="L1201" t="n">
+        <v>-3007.15854</v>
+      </c>
+      <c r="M1201" t="n">
+        <v>52459.68667179618</v>
+      </c>
+      <c r="N1201" t="n">
+        <v>55466.84521179618</v>
+      </c>
+      <c r="O1201" t="n">
+        <v>8572781208</v>
+      </c>
+      <c r="P1201" t="n">
+        <v>714363025</v>
+      </c>
+      <c r="Q1201" t="n">
+        <v>353048769</v>
+      </c>
+      <c r="R1201" t="n">
+        <v>4928161403</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1202" t="n">
+        <v>49.2471</v>
+      </c>
+      <c r="C1202" t="n">
+        <v>175873.2934528124</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>107008.1402781</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>175873.2934528124</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>52348.11930042581</v>
+      </c>
+      <c r="G1202" t="n">
+        <v>14576.98083745033</v>
+      </c>
+      <c r="H1202" t="n">
+        <v>7184.256210010335</v>
+      </c>
+      <c r="I1202" t="n">
+        <v>101763.937104926</v>
+      </c>
+      <c r="J1202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1202" t="n">
+        <v>3207.59145</v>
+      </c>
+      <c r="L1202" t="n">
+        <v>-3207.59145</v>
+      </c>
+      <c r="M1202" t="n">
+        <v>52348.11930042581</v>
+      </c>
+      <c r="N1202" t="n">
+        <v>55555.71075042581</v>
+      </c>
+      <c r="O1202" t="n">
+        <v>8661249670</v>
+      </c>
+      <c r="P1202" t="n">
+        <v>717874033</v>
+      </c>
+      <c r="Q1202" t="n">
+        <v>353803784</v>
+      </c>
+      <c r="R1202" t="n">
+        <v>5011578787</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1203" t="n">
+        <v>49.2794</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>171875.4860854637</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>107008.1402781</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>171875.4860854637</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>47278.00882315937</v>
+      </c>
+      <c r="G1203" t="n">
+        <v>14563.29255226322</v>
+      </c>
+      <c r="H1203" t="n">
+        <v>7058.048291984074</v>
+      </c>
+      <c r="I1203" t="n">
+        <v>102976.136418057</v>
+      </c>
+      <c r="J1203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1203" t="n">
+        <v>3414.665</v>
+      </c>
+      <c r="L1203" t="n">
+        <v>-3414.665</v>
+      </c>
+      <c r="M1203" t="n">
+        <v>47278.00882315937</v>
+      </c>
+      <c r="N1203" t="n">
+        <v>50692.67382315937</v>
+      </c>
+      <c r="O1203" t="n">
+        <v>8469920829</v>
+      </c>
+      <c r="P1203" t="n">
+        <v>717670319</v>
+      </c>
+      <c r="Q1203" t="n">
+        <v>347816385</v>
+      </c>
+      <c r="R1203" t="n">
+        <v>5074602217</v>
       </c>
     </row>
   </sheetData>
@@ -67604,7 +67828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D249"/>
+  <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71101,6 +71325,20 @@
         <v>167387.7467076</v>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B250" t="n">
+        <v>107008.1402781</v>
+      </c>
+      <c r="C250" t="n">
+        <v>64566.812263</v>
+      </c>
+      <c r="D250" t="n">
+        <v>171574.9525411</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1204"/>
+  <dimension ref="A1:R1208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67871,6 +67871,230 @@
       </c>
       <c r="R1204" t="n">
         <v>5091207930</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1205" t="n">
+        <v>49.3315</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>171285.5970323221</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>106948.8458287</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>171285.5970323221</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>46095.97780322915</v>
+      </c>
+      <c r="G1205" t="n">
+        <v>14498.57150096794</v>
+      </c>
+      <c r="H1205" t="n">
+        <v>7154.08763163496</v>
+      </c>
+      <c r="I1205" t="n">
+        <v>103536.9600964901</v>
+      </c>
+      <c r="J1205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1205" t="n">
+        <v>4316.87425</v>
+      </c>
+      <c r="L1205" t="n">
+        <v>-4316.87425</v>
+      </c>
+      <c r="M1205" t="n">
+        <v>46095.97780322915</v>
+      </c>
+      <c r="N1205" t="n">
+        <v>50412.85205322915</v>
+      </c>
+      <c r="O1205" t="n">
+        <v>8449775430</v>
+      </c>
+      <c r="P1205" t="n">
+        <v>715236280</v>
+      </c>
+      <c r="Q1205" t="n">
+        <v>352921874</v>
+      </c>
+      <c r="R1205" t="n">
+        <v>5107633547</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1206" t="n">
+        <v>49.3573</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>170805.2278386378</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>106948.8458287</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>170805.2278386378</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>44615.34399166889</v>
+      </c>
+      <c r="G1206" t="n">
+        <v>14567.45081274705</v>
+      </c>
+      <c r="H1206" t="n">
+        <v>7115.481397888459</v>
+      </c>
+      <c r="I1206" t="n">
+        <v>104506.9516363334</v>
+      </c>
+      <c r="J1206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1206" t="n">
+        <v>4254.80446</v>
+      </c>
+      <c r="L1206" t="n">
+        <v>-4254.80446</v>
+      </c>
+      <c r="M1206" t="n">
+        <v>44615.34399166889</v>
+      </c>
+      <c r="N1206" t="n">
+        <v>48870.14845166889</v>
+      </c>
+      <c r="O1206" t="n">
+        <v>8430484872</v>
+      </c>
+      <c r="P1206" t="n">
+        <v>719010040</v>
+      </c>
+      <c r="Q1206" t="n">
+        <v>351200950</v>
+      </c>
+      <c r="R1206" t="n">
+        <v>5158180964</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1207" t="n">
+        <v>49.4632</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>170654.5357760921</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>106948.8458287</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>170654.5357760921</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>43843.71997768036</v>
+      </c>
+      <c r="G1207" t="n">
+        <v>14492.84924954309</v>
+      </c>
+      <c r="H1207" t="n">
+        <v>7061.932931957495</v>
+      </c>
+      <c r="I1207" t="n">
+        <v>105256.0336169112</v>
+      </c>
+      <c r="J1207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1207" t="n">
+        <v>4467.34245</v>
+      </c>
+      <c r="L1207" t="n">
+        <v>-4467.34245</v>
+      </c>
+      <c r="M1207" t="n">
+        <v>43843.71997768036</v>
+      </c>
+      <c r="N1207" t="n">
+        <v>48311.06242768036</v>
+      </c>
+      <c r="O1207" t="n">
+        <v>8441119434</v>
+      </c>
+      <c r="P1207" t="n">
+        <v>716862701</v>
+      </c>
+      <c r="Q1207" t="n">
+        <v>349305801</v>
+      </c>
+      <c r="R1207" t="n">
+        <v>5206300242</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1208" t="n">
+        <v>49.4889</v>
+      </c>
+      <c r="C1208" t="n">
+        <v>170658.3568032428</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>106948.8458287</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>170658.3568032428</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>43631.49352683127</v>
+      </c>
+      <c r="G1208" t="n">
+        <v>14562.24143191706</v>
+      </c>
+      <c r="H1208" t="n">
+        <v>7098.190503324989</v>
+      </c>
+      <c r="I1208" t="n">
+        <v>105366.4313411694</v>
+      </c>
+      <c r="J1208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1208" t="n">
+        <v>4366.26217</v>
+      </c>
+      <c r="L1208" t="n">
+        <v>-4366.26217</v>
+      </c>
+      <c r="M1208" t="n">
+        <v>43631.49352683127</v>
+      </c>
+      <c r="N1208" t="n">
+        <v>47997.75569683127</v>
+      </c>
+      <c r="O1208" t="n">
+        <v>8445694354</v>
+      </c>
+      <c r="P1208" t="n">
+        <v>720669310</v>
+      </c>
+      <c r="Q1208" t="n">
+        <v>351281640</v>
+      </c>
+      <c r="R1208" t="n">
+        <v>5214468784</v>
       </c>
     </row>
   </sheetData>
@@ -67884,7 +68108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D250"/>
+  <dimension ref="A1:D251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71395,6 +71619,20 @@
         <v>171574.9525411</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B251" t="n">
+        <v>106948.8458287</v>
+      </c>
+      <c r="C251" t="n">
+        <v>62147.667089</v>
+      </c>
+      <c r="D251" t="n">
+        <v>169096.5129177</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/net_rezerv.xlsx
+++ b/net rezerv/net_rezerv.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1212"/>
+  <dimension ref="A1:R1213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68164,7 +68164,7 @@
         <v>164442.8834108145</v>
       </c>
       <c r="D1210" t="n">
-        <v>106948.8458287</v>
+        <v>103146.0577849</v>
       </c>
       <c r="E1210" t="n">
         <v>164442.8834108145</v>
@@ -68220,7 +68220,7 @@
         <v>162203.2255617405</v>
       </c>
       <c r="D1211" t="n">
-        <v>106948.8458287</v>
+        <v>103146.0577849</v>
       </c>
       <c r="E1211" t="n">
         <v>162203.2255617405</v>
@@ -68276,7 +68276,7 @@
         <v>162241.4895758679</v>
       </c>
       <c r="D1212" t="n">
-        <v>106948.8458287</v>
+        <v>103146.0577849</v>
       </c>
       <c r="E1212" t="n">
         <v>162241.4895758679</v>
@@ -68319,6 +68319,62 @@
       </c>
       <c r="R1212" t="n">
         <v>5247672806</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1213" t="n">
+        <v>49.6997</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>162971.7459662734</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>103146.0577849</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>162971.7459662734</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>35741.08314537109</v>
+      </c>
+      <c r="G1213" t="n">
+        <v>14365.46280963466</v>
+      </c>
+      <c r="H1213" t="n">
+        <v>6754.548558643211</v>
+      </c>
+      <c r="I1213" t="n">
+        <v>106110.6514526245</v>
+      </c>
+      <c r="J1213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1213" t="n">
+        <v>3758.02536</v>
+      </c>
+      <c r="L1213" t="n">
+        <v>-3758.02536</v>
+      </c>
+      <c r="M1213" t="n">
+        <v>35741.08314537109</v>
+      </c>
+      <c r="N1213" t="n">
+        <v>39499.10850537108</v>
+      </c>
+      <c r="O1213" t="n">
+        <v>8099646883</v>
+      </c>
+      <c r="P1213" t="n">
+        <v>713959192</v>
+      </c>
+      <c r="Q1213" t="n">
+        <v>335699037</v>
+      </c>
+      <c r="R1213" t="n">
+        <v>5273667544</v>
       </c>
     </row>
   </sheetData>
@@ -68332,7 +68388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D251"/>
+  <dimension ref="A1:D252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71857,6 +71913,20 @@
         <v>169096.5129177</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B252" t="n">
+        <v>103146.0577849</v>
+      </c>
+      <c r="C252" t="n">
+        <v>59044.8569306</v>
+      </c>
+      <c r="D252" t="n">
+        <v>162190.9147155</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
